--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127834597</v>
       </c>
       <c r="B2" t="n">
-        <v>58306</v>
+        <v>58309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,57 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127834644</v>
+        <v>127834132</v>
       </c>
       <c r="B3" t="n">
-        <v>57676</v>
+        <v>105409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600421</v>
+        <v>600357</v>
       </c>
       <c r="R3" t="n">
-        <v>6365452</v>
+        <v>6365492</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,63 +860,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127834132</v>
+        <v>127834644</v>
       </c>
       <c r="B4" t="n">
-        <v>105406</v>
+        <v>57679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600357</v>
+        <v>600421</v>
       </c>
       <c r="R4" t="n">
-        <v>6365492</v>
+        <v>6365452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,19 +970,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -991,7 +991,7 @@
         <v>127834133</v>
       </c>
       <c r="B5" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127834567</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>127835957</v>
       </c>
       <c r="B7" t="n">
-        <v>110550</v>
+        <v>110553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>127834134</v>
       </c>
       <c r="B8" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127834646</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127834597</v>
       </c>
       <c r="B2" t="n">
-        <v>58309</v>
+        <v>58315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,45 +781,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127834132</v>
+        <v>127834644</v>
       </c>
       <c r="B3" t="n">
-        <v>105409</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600357</v>
+        <v>600421</v>
       </c>
       <c r="R3" t="n">
-        <v>6365492</v>
+        <v>6365452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -846,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -860,76 +872,63 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127834644</v>
+        <v>127834132</v>
       </c>
       <c r="B4" t="n">
-        <v>57679</v>
+        <v>105417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600421</v>
+        <v>600357</v>
       </c>
       <c r="R4" t="n">
-        <v>6365452</v>
+        <v>6365492</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,18 +969,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -991,7 +991,7 @@
         <v>127834133</v>
       </c>
       <c r="B5" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127834567</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
         <v>127835957</v>
       </c>
       <c r="B7" t="n">
-        <v>110553</v>
+        <v>110561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>127834134</v>
       </c>
       <c r="B8" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127834646</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>127834132</v>
       </c>
       <c r="B4" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>127834133</v>
       </c>
       <c r="B5" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
         <v>127835957</v>
       </c>
       <c r="B7" t="n">
-        <v>110561</v>
+        <v>110562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>127834134</v>
       </c>
       <c r="B8" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -781,57 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127834644</v>
+        <v>127834132</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>105418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600421</v>
+        <v>600357</v>
       </c>
       <c r="R3" t="n">
-        <v>6365452</v>
+        <v>6365492</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,63 +860,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127834132</v>
+        <v>127834644</v>
       </c>
       <c r="B4" t="n">
-        <v>105418</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600357</v>
+        <v>600421</v>
       </c>
       <c r="R4" t="n">
-        <v>6365492</v>
+        <v>6365452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,19 +970,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127834132</v>
       </c>
       <c r="B3" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>127834133</v>
       </c>
       <c r="B5" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>127835957</v>
       </c>
       <c r="B7" t="n">
-        <v>110562</v>
+        <v>110563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
         <v>127834134</v>
       </c>
       <c r="B8" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127834132</v>
       </c>
       <c r="B3" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>127834133</v>
       </c>
       <c r="B5" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>127835957</v>
       </c>
       <c r="B7" t="n">
-        <v>110563</v>
+        <v>110564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>127834134</v>
       </c>
       <c r="B8" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -781,45 +781,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127834132</v>
+        <v>127834644</v>
       </c>
       <c r="B3" t="n">
-        <v>105420</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600357</v>
+        <v>600421</v>
       </c>
       <c r="R3" t="n">
-        <v>6365492</v>
+        <v>6365452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -846,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -860,76 +872,63 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127834644</v>
+        <v>127834132</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>105420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600421</v>
+        <v>600357</v>
       </c>
       <c r="R4" t="n">
-        <v>6365452</v>
+        <v>6365492</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,18 +969,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1085,57 +1085,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127834567</v>
+        <v>127835957</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>110564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600425</v>
+        <v>600357</v>
       </c>
       <c r="R6" t="n">
-        <v>6365545</v>
+        <v>6365478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,12 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,57 +1170,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835957</v>
+        <v>127834567</v>
       </c>
       <c r="B7" t="n">
-        <v>110564</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600357</v>
+        <v>600425</v>
       </c>
       <c r="R7" t="n">
-        <v>6365478</v>
+        <v>6365545</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -781,57 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127834644</v>
+        <v>127834132</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>105420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600421</v>
+        <v>600357</v>
       </c>
       <c r="R3" t="n">
-        <v>6365452</v>
+        <v>6365492</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,63 +860,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127834132</v>
+        <v>127834644</v>
       </c>
       <c r="B4" t="n">
-        <v>105420</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600357</v>
+        <v>600421</v>
       </c>
       <c r="R4" t="n">
-        <v>6365492</v>
+        <v>6365452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,19 +970,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1085,45 +1085,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127835957</v>
+        <v>127834567</v>
       </c>
       <c r="B6" t="n">
-        <v>110564</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600357</v>
+        <v>600425</v>
       </c>
       <c r="R6" t="n">
-        <v>6365478</v>
+        <v>6365545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,12 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,69 +1182,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127834567</v>
+        <v>127835957</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>110564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600425</v>
+        <v>600357</v>
       </c>
       <c r="R7" t="n">
-        <v>6365545</v>
+        <v>6365478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -781,45 +781,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127834132</v>
+        <v>127834644</v>
       </c>
       <c r="B3" t="n">
-        <v>105420</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600357</v>
+        <v>600421</v>
       </c>
       <c r="R3" t="n">
-        <v>6365492</v>
+        <v>6365452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -846,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -860,76 +872,63 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127834644</v>
+        <v>127834132</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>105420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600421</v>
+        <v>600357</v>
       </c>
       <c r="R4" t="n">
-        <v>6365452</v>
+        <v>6365492</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,18 +969,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1085,57 +1085,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127834567</v>
+        <v>127835957</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>110564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600425</v>
+        <v>600357</v>
       </c>
       <c r="R6" t="n">
-        <v>6365545</v>
+        <v>6365478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,12 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,57 +1170,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835957</v>
+        <v>127834567</v>
       </c>
       <c r="B7" t="n">
-        <v>110564</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600357</v>
+        <v>600425</v>
       </c>
       <c r="R7" t="n">
-        <v>6365478</v>
+        <v>6365545</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127834597</v>
       </c>
       <c r="B2" t="n">
-        <v>58315</v>
+        <v>58316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127834644</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127834132</v>
       </c>
       <c r="B4" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>127834133</v>
       </c>
       <c r="B5" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,45 +1085,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127835957</v>
+        <v>127834567</v>
       </c>
       <c r="B6" t="n">
-        <v>110564</v>
+        <v>57670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600357</v>
+        <v>600425</v>
       </c>
       <c r="R6" t="n">
-        <v>6365478</v>
+        <v>6365545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,12 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,69 +1182,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127834567</v>
+        <v>127835957</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>110572</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600425</v>
+        <v>600357</v>
       </c>
       <c r="R7" t="n">
-        <v>6365545</v>
+        <v>6365478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
         <v>127834134</v>
       </c>
       <c r="B8" t="n">
-        <v>105420</v>
+        <v>105428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127834646</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127834597</v>
       </c>
       <c r="B2" t="n">
-        <v>58316</v>
+        <v>58328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127834644</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57698</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127834132</v>
       </c>
       <c r="B4" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>127834133</v>
       </c>
       <c r="B5" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,57 +1085,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127834567</v>
+        <v>127835957</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>110665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600425</v>
+        <v>600357</v>
       </c>
       <c r="R6" t="n">
-        <v>6365545</v>
+        <v>6365478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,12 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,57 +1170,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835957</v>
+        <v>127834567</v>
       </c>
       <c r="B7" t="n">
-        <v>110572</v>
+        <v>57682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600357</v>
+        <v>600425</v>
       </c>
       <c r="R7" t="n">
-        <v>6365478</v>
+        <v>6365545</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,7 +1279,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1294,7 +1294,7 @@
         <v>127834134</v>
       </c>
       <c r="B8" t="n">
-        <v>105428</v>
+        <v>105521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127834646</v>
       </c>
       <c r="B9" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1085,45 +1085,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127835957</v>
+        <v>127834567</v>
       </c>
       <c r="B6" t="n">
-        <v>110665</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600357</v>
+        <v>600425</v>
       </c>
       <c r="R6" t="n">
-        <v>6365478</v>
+        <v>6365545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,12 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,69 +1182,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127834567</v>
+        <v>127835957</v>
       </c>
       <c r="B7" t="n">
-        <v>57682</v>
+        <v>110665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600425</v>
+        <v>600357</v>
       </c>
       <c r="R7" t="n">
-        <v>6365545</v>
+        <v>6365478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,7 +1279,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1085,57 +1085,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127834567</v>
+        <v>127835957</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>110665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600425</v>
+        <v>600357</v>
       </c>
       <c r="R6" t="n">
-        <v>6365545</v>
+        <v>6365478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,12 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,57 +1170,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835957</v>
+        <v>127834567</v>
       </c>
       <c r="B7" t="n">
-        <v>110665</v>
+        <v>57682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600357</v>
+        <v>600425</v>
       </c>
       <c r="R7" t="n">
-        <v>6365478</v>
+        <v>6365545</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1496,6 +1496,127 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130826523</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56528</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>600405</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6365471</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hasselmusbo i örnbräken,  ~8cm diameter</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127834597</v>
+        <v>127834136</v>
       </c>
       <c r="B2" t="n">
-        <v>58328</v>
+        <v>107256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kritsuga</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Ajuga genevensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600351</v>
+        <v>600336</v>
       </c>
       <c r="R2" t="n">
-        <v>6365493</v>
+        <v>6365503</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,32 +740,38 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>troligen inte men värt att gå tillbaka och kolla när den vuxit på sig lite.</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,7 +781,7 @@
         <v>127834644</v>
       </c>
       <c r="B3" t="n">
-        <v>57698</v>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127834132</v>
+        <v>127834567</v>
       </c>
       <c r="B4" t="n">
-        <v>105521</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,34 +898,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600357</v>
+        <v>600425</v>
       </c>
       <c r="R4" t="n">
-        <v>6365492</v>
+        <v>6365545</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,29 +978,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127834133</v>
+        <v>127834646</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,34 +1007,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600354</v>
+        <v>600493</v>
       </c>
       <c r="R5" t="n">
-        <v>6365500</v>
+        <v>6365582</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,12 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,22 +1093,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127835957</v>
+        <v>130826523</v>
       </c>
       <c r="B6" t="n">
-        <v>110665</v>
+        <v>56614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,34 +1116,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>100084</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600357</v>
+        <v>600405</v>
       </c>
       <c r="R6" t="n">
-        <v>6365478</v>
+        <v>6365471</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,12 +1189,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hasselmusbo i örnbräken,  ~8cm diameter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,39 +1214,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127834567</v>
+        <v>127834594</v>
       </c>
       <c r="B7" t="n">
-        <v>57682</v>
+        <v>58286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1219,7 +1263,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1229,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600425</v>
+        <v>600724</v>
       </c>
       <c r="R7" t="n">
-        <v>6365545</v>
+        <v>6365663</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,52 +1328,61 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127834134</v>
+        <v>127834597</v>
       </c>
       <c r="B8" t="n">
-        <v>105521</v>
+        <v>58602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600352</v>
+        <v>600351</v>
       </c>
       <c r="R8" t="n">
-        <v>6365506</v>
+        <v>6365493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1409,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1370,29 +1423,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127834646</v>
+        <v>127835957</v>
       </c>
       <c r="B9" t="n">
-        <v>57682</v>
+        <v>111390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,46 +1452,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600493</v>
+        <v>600357</v>
       </c>
       <c r="R9" t="n">
-        <v>6365582</v>
+        <v>6365478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,12 +1506,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,22 +1526,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130826523</v>
+        <v>127834130</v>
       </c>
       <c r="B10" t="n">
-        <v>56548</v>
+        <v>106156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1509,53 +1549,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100084</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600405</v>
+        <v>600345</v>
       </c>
       <c r="R10" t="n">
-        <v>6365471</v>
+        <v>6365475</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,17 +1603,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hasselmusbo i örnbräken,  ~8cm diameter</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,21 +1617,709 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127834131</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>600354</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6365478</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127834132</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>600357</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6365492</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127834134</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>600352</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6365506</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127834235</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>600340</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6365481</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Louise Lindroth, Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127834133</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>600354</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6365500</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127834135</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>600339</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6365499</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127834157</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>600540</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6365576</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834644</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834567</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834646</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826523</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834594</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834597</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127835957</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834130</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834131</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834132</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1927,6 +1987,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834134</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2029,6 +2094,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834235</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2126,6 +2196,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834133</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2223,6 +2298,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834135</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,8 +2400,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834157</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127834594</v>
+        <v>136039724</v>
       </c>
       <c r="B7" t="n">
-        <v>58286</v>
+        <v>57783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>102118</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1289,27 +1289,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600724</v>
+        <v>600376</v>
       </c>
       <c r="R7" t="n">
-        <v>6365663</v>
+        <v>6365429</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,12 +1335,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,33 +1366,33 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834594</t>
+          <t>https://artportalen.se/Sighting/136039724</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127834597</v>
+        <v>127834594</v>
       </c>
       <c r="B8" t="n">
-        <v>58602</v>
+        <v>58286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1403,21 +1405,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600351</v>
+        <v>600724</v>
       </c>
       <c r="R8" t="n">
-        <v>6365493</v>
+        <v>6365663</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,51 +1480,60 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834597</t>
+          <t>https://artportalen.se/Sighting/127834594</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127835957</v>
+        <v>127834597</v>
       </c>
       <c r="B9" t="n">
-        <v>111390</v>
+        <v>58602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>103042</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600357</v>
+        <v>600351</v>
       </c>
       <c r="R9" t="n">
-        <v>6365478</v>
+        <v>6365493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,12 +1560,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,44 +1580,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127835957</t>
+          <t>https://artportalen.se/Sighting/127834597</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127834130</v>
+        <v>127835957</v>
       </c>
       <c r="B10" t="n">
-        <v>106156</v>
+        <v>111390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1618,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600345</v>
+        <v>600357</v>
       </c>
       <c r="R10" t="n">
-        <v>6365475</v>
+        <v>6365478</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,12 +1662,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,7 +1676,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1674,19 +1687,19 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834130</t>
+          <t>https://artportalen.se/Sighting/127835957</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127834131</v>
+        <v>127834130</v>
       </c>
       <c r="B11" t="n">
         <v>106156</v>
@@ -1721,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600354</v>
+        <v>600345</v>
       </c>
       <c r="R11" t="n">
-        <v>6365478</v>
+        <v>6365475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,13 +1796,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834131</t>
+          <t>https://artportalen.se/Sighting/127834130</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127834132</v>
+        <v>127834131</v>
       </c>
       <c r="B12" t="n">
         <v>106156</v>
@@ -1824,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600357</v>
+        <v>600354</v>
       </c>
       <c r="R12" t="n">
-        <v>6365492</v>
+        <v>6365478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,13 +1899,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834132</t>
+          <t>https://artportalen.se/Sighting/127834131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127834134</v>
+        <v>127834132</v>
       </c>
       <c r="B13" t="n">
         <v>106156</v>
@@ -1927,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600352</v>
+        <v>600357</v>
       </c>
       <c r="R13" t="n">
-        <v>6365506</v>
+        <v>6365492</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,13 +2002,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834134</t>
+          <t>https://artportalen.se/Sighting/127834132</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127834235</v>
+        <v>127834134</v>
       </c>
       <c r="B14" t="n">
         <v>106156</v>
@@ -2030,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600340</v>
+        <v>600352</v>
       </c>
       <c r="R14" t="n">
-        <v>6365481</v>
+        <v>6365506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,17 +2073,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,6 +2087,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2090,22 +2099,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834235</t>
+          <t>https://artportalen.se/Sighting/127834134</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127834133</v>
+        <v>127834235</v>
       </c>
       <c r="B15" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,21 +2122,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2137,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600354</v>
+        <v>600340</v>
       </c>
       <c r="R15" t="n">
-        <v>6365500</v>
+        <v>6365481</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,12 +2176,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,19 +2206,19 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834133</t>
+          <t>https://artportalen.se/Sighting/127834235</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127834135</v>
+        <v>127834133</v>
       </c>
       <c r="B16" t="n">
         <v>101326</v>
@@ -2239,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600339</v>
+        <v>600354</v>
       </c>
       <c r="R16" t="n">
-        <v>6365499</v>
+        <v>6365500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,13 +2314,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834135</t>
+          <t>https://artportalen.se/Sighting/127834133</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127834157</v>
+        <v>127834135</v>
       </c>
       <c r="B17" t="n">
         <v>101326</v>
@@ -2341,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600540</v>
+        <v>600339</v>
       </c>
       <c r="R17" t="n">
-        <v>6365576</v>
+        <v>6365499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,12 +2385,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,6 +2415,108 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834135</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127834157</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>600540</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6365576</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127834157</t>
         </is>
@@ -2424,6 +2540,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,45 +1597,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127835957</v>
+        <v>136125153</v>
       </c>
       <c r="B10" t="n">
-        <v>111390</v>
+        <v>58819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>208245</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ävrö, Sm</t>
+          <t>Sörö, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600357</v>
+        <v>600332</v>
       </c>
       <c r="R10" t="n">
-        <v>6365478</v>
+        <v>6365561</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,12 +1675,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,44 +1705,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127835957</t>
+          <t>https://artportalen.se/Sighting/136125153</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127834130</v>
+        <v>127835957</v>
       </c>
       <c r="B11" t="n">
-        <v>106156</v>
+        <v>111390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1734,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600345</v>
+        <v>600357</v>
       </c>
       <c r="R11" t="n">
-        <v>6365475</v>
+        <v>6365478</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1764,12 +1787,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,7 +1801,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1790,19 +1812,19 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834130</t>
+          <t>https://artportalen.se/Sighting/127835957</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127834131</v>
+        <v>127834130</v>
       </c>
       <c r="B12" t="n">
         <v>106156</v>
@@ -1837,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600354</v>
+        <v>600345</v>
       </c>
       <c r="R12" t="n">
-        <v>6365478</v>
+        <v>6365475</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,13 +1921,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834131</t>
+          <t>https://artportalen.se/Sighting/127834130</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127834132</v>
+        <v>127834131</v>
       </c>
       <c r="B13" t="n">
         <v>106156</v>
@@ -1940,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600357</v>
+        <v>600354</v>
       </c>
       <c r="R13" t="n">
-        <v>6365492</v>
+        <v>6365478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,13 +2024,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834132</t>
+          <t>https://artportalen.se/Sighting/127834131</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127834134</v>
+        <v>127834132</v>
       </c>
       <c r="B14" t="n">
         <v>106156</v>
@@ -2043,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600352</v>
+        <v>600357</v>
       </c>
       <c r="R14" t="n">
-        <v>6365506</v>
+        <v>6365492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,13 +2127,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834134</t>
+          <t>https://artportalen.se/Sighting/127834132</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127834235</v>
+        <v>127834134</v>
       </c>
       <c r="B15" t="n">
         <v>106156</v>
@@ -2146,10 +2168,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600340</v>
+        <v>600352</v>
       </c>
       <c r="R15" t="n">
-        <v>6365481</v>
+        <v>6365506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,17 +2198,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,6 +2212,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2206,22 +2224,22 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834235</t>
+          <t>https://artportalen.se/Sighting/127834134</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127834133</v>
+        <v>127834235</v>
       </c>
       <c r="B16" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2253,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600354</v>
+        <v>600340</v>
       </c>
       <c r="R16" t="n">
-        <v>6365500</v>
+        <v>6365481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,12 +2301,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,19 +2331,19 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834133</t>
+          <t>https://artportalen.se/Sighting/127834235</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127834135</v>
+        <v>127834133</v>
       </c>
       <c r="B17" t="n">
         <v>101326</v>
@@ -2355,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600339</v>
+        <v>600354</v>
       </c>
       <c r="R17" t="n">
-        <v>6365499</v>
+        <v>6365500</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,13 +2439,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834135</t>
+          <t>https://artportalen.se/Sighting/127834133</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127834157</v>
+        <v>127834135</v>
       </c>
       <c r="B18" t="n">
         <v>101326</v>
@@ -2457,10 +2480,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600540</v>
+        <v>600339</v>
       </c>
       <c r="R18" t="n">
-        <v>6365576</v>
+        <v>6365499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,12 +2510,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,6 +2540,108 @@
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834135</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127834157</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>600540</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6365576</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127834157</t>
         </is>
@@ -2541,6 +2666,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>136039724</v>
       </c>
       <c r="B7" t="n">
-        <v>57783</v>
+        <v>57784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>136125153</v>
       </c>
       <c r="B10" t="n">
-        <v>58819</v>
+        <v>58820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>136039724</v>
       </c>
       <c r="B7" t="n">
-        <v>57784</v>
+        <v>57788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>136125153</v>
       </c>
       <c r="B10" t="n">
-        <v>58820</v>
+        <v>58824</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>136039724</v>
       </c>
       <c r="B7" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>136125153</v>
       </c>
       <c r="B10" t="n">
-        <v>58824</v>
+        <v>58825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>136039724</v>
       </c>
       <c r="B7" t="n">
-        <v>57789</v>
+        <v>57794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>136125153</v>
       </c>
       <c r="B10" t="n">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>136039724</v>
       </c>
       <c r="B7" t="n">
-        <v>57794</v>
+        <v>57807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>136125153</v>
       </c>
       <c r="B10" t="n">
-        <v>58830</v>
+        <v>58843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
